--- a/medford_kosmetologiya_v2.xlsx
+++ b/medford_kosmetologiya_v2.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -755,32 +755,49 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Заполнить вручную</t>
+          <t>Характеристики товаров</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Характеристики товаров, страна, наличие, РУ, цены, кейсы, ФИО автора, телефон</t>
+          <t>Заполнены с карточек товаров medford.ru (технологии, параметры, гарантия)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Проставлены плейсхолдеры [ ] / «уточнять» — брать с карточек товаров и из данных компании</t>
+          <t>Solalux/Esther/Pinacle/Curelux — реальные ТТХ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Заполнить вручную</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Страна производства, наличие, статус РУ Росздравнадзора, цены, кейсы, ФИО автора, телефон</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>На страницах не указаны — плейсхолдеры [ ] / «уточнять»</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>URL раздела</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>https://medford.ru/catalog/kosmetologiya/</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>SECTION_CODE = kosmetologiya · 4 подкатегории</t>
         </is>
@@ -4070,12 +4087,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Лазер (многофункциональная система)</t>
+          <t>Лазер (александрит 755 нм + Nd:YAG 1064 нм)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Эпиляция, омоложение, лечение кожи</t>
+          <t>Эпиляция всех фототипов, сосудистые патологии, пигментация, омоложение, стрии, рубцы</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4111,12 +4128,12 @@
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>[Заполнить с карточки товара на medford.ru]</t>
+          <t>Гибридная платформа: александрит 755 нм + Nd:YAG 1064 нм в одной манипуле|Технология Hybrid Alex/Nd:YAG — одновременная подача двух длин волн|7 размеров светового пятна без замены насадок (расходники до −40%)|Режимы: Alexandrite 755, Nd:YAG 1064, Hybrid 755/1064; Smart Mode|Задачи: эпиляция, сосудистые, пигментация, омоложение, стрии, рубцы, онихомикоз</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Многофункциональная лазерная система — комбинированные процедуры</t>
+          <t>Гибридная лазерная система: александрит 755 нм + Nd:YAG 1064 нм</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
@@ -4174,12 +4191,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>IPL (интенсивный импульсный свет)</t>
+          <t>IPL / FPL (фракционный импульсный свет)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Фотоомоложение, лечение акне, пигментации, эпиляция</t>
+          <t>Фотоомоложение, сосудистые, пигментация, акне/постакне, эпиляция (I–III фототип)</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4204,7 +4221,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>уточнять</t>
+          <t>до 24 месяцев</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -4215,12 +4232,12 @@
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>[Заполнить с карточки товара на medford.ru]</t>
+          <t>Фракционный IPL/FPL, технология 140 multi-cell|Флюенс 1–32 Дж/см², импульс 0,2–40 мс, пятно 42,6 × 14,3 мм|7 экспертных фильтров: 415/530/560/590/640/690/755 нм|Режимы Stamp и In-motion; встроенные SMART-протоколы|Задачи: сосудистые, пигментация, акне/постакне, термолифтинг, эпиляция</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>IPL-аппарат — фототерапия и фотоомоложение</t>
+          <t>Фракционный IPL/FPL-аппарат для фотоомоложения и коррекции кожи</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -4278,12 +4295,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>RF (радиочастотный лифтинг)</t>
+          <t>Микроигольчатый RF (MNRF)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Подтяжка кожи, стимуляция коллагена</t>
+          <t>Термолифтинг, ремоделирование кожи, рубцы постакне, морщины, стрии, дряблость</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4308,7 +4325,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>уточнять</t>
+          <t>24 месяца</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -4319,12 +4336,12 @@
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>[Заполнить с карточки товара на medford.ru]</t>
+          <t>Микроигольчатый RF (MNRF), частота 1 и 2 МГц, мощность 40 Вт|Технология DOUBLE Shot; встроенные SMART-протоколы|3 типа картриджей: изолир./неизолир. иглы 36 pin, глубина 0,5–4 мм; неинвазивные электроды|Шаг глубины 0,1 мм, ресурс картриджа 3000 проколов; процедура 15–20 мин|Задачи: постакне и рубцы, морщины, стрии, дряблость, локальный гипергидроз</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Аппарат для RF-лифтинга — радиочастотная подтяжка кожи</t>
+          <t>Микроигольчатый RF-аппарат для фракционного термолифтинга и ремоделирования кожи</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -4382,12 +4399,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Фототерапия (фотобиомодуляция, PDT)</t>
+          <t>LED-фототерапия (ФБМ + ФДТ)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Фотобиомодуляция, фотодинамическая терапия, регенерация</t>
+          <t>Восстановление после процедур, акне/розацеа, заживление ран, anti-age, трихология</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4423,12 +4440,12 @@
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>[Заполнить с карточки товара на medford.ru]</t>
+          <t>Светодиодная фототерапия: фотобиомодуляция (ФБМ) + фотодинамическая терапия (ФДТ)|4 длины волны: 415 (синий), 585 (жёлтый), 635 (красный), 830 нм (ИК)|Mix-протокол — до 3 длин волн одновременно; матрица линз OML|SMART-протоколы; процедура 10–50 мин; 0 ₽ на расходники|Задачи: акне/розацеа, трихология, заживление ран, восстановление, anti-age</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Фотобиомодуляция и фотодинамическая терапия (PDT)</t>
+          <t>Светодиодная система для фотобиомодуляции и фотодинамической терапии</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -4440,7 +4457,7 @@
     <row r="9">
       <c r="E9" t="inlineStr">
         <is>
-          <t>Все 4 товара — из живого каталога medford.ru на дату страницы. Бренд Decotica, цена «по запросу». Спецификации, страна, наличие и РУ — заполнить с карточек товаров (на странице категории их нет).</t>
+          <t>Все 4 товара — из живого каталога medford.ru. Бренд Decotica, цена «по запросу». Характеристики и гарантия — с карточек товаров. Осталось уточнить только страну производства, наличие и статус РУ Росздравнадзора (на страницах не указаны).</t>
         </is>
       </c>
     </row>
@@ -4617,12 +4634,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Лазер (многофункц.)</t>
+          <t>Лазер Alex 755 + Nd:YAG 1064</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Эпиляция, омоложение, лечение кожи</t>
+          <t>Эпиляция, сосудистые, пигментация, омоложение</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4637,7 +4654,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>от 12 мес</t>
+          <t>уточнять</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -4695,12 +4712,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IPL / FPL (140 multi-cell)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Фотоомоложение, акне, пигментация, эпиляция</t>
+          <t>Фотоомоложение, акне, пигментация, сосудистые, эпиляция</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -4715,7 +4732,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>от 12 мес</t>
+          <t>до 24 мес</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -4773,12 +4790,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>Микроигольчатый RF (MNRF)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Подтяжка кожи, стимуляция коллагена</t>
+          <t>Термолифтинг, рубцы постакне, морщины, стрии</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -4793,7 +4810,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>от 12 мес</t>
+          <t>24 мес</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -4851,12 +4868,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Фотобиомодуляция / PDT</t>
+          <t>LED-фототерапия (ФБМ + ФДТ)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Регенерация, фотодинамическая терапия</t>
+          <t>Восстановление, акне/розацеа, заживление, anti-age</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -4871,7 +4888,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>от 12 мес</t>
+          <t>уточнять</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">

--- a/medford_kosmetologiya_v2.xlsx
+++ b/medford_kosmetologiya_v2.xlsx
@@ -777,12 +777,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Страна производства, наличие, статус РУ Росздравнадзора, цены, кейсы, ФИО автора, телефон</t>
+          <t>Страна производства, наличие, статус РУ Росздравнадзора, цены, кейсы (08_CASES)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>На страницах не указаны — плейсхолдеры [ ] / «уточнять»</t>
+          <t>На страницах не указаны — плейсхолдеры [ ] / «уточнять». ФИО автора — рандомный, заменить</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>[ФИО автора]</t>
+          <t>Марина Ковалёва</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Товары — реальный каталог medford.ru (4 модели Decotica); тексты — триплеты SERP</t>
+          <t>ФИО автора — рандомный плейсхолдер, заменить вручную. Товары — реальный каталог medford.ru</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>[ФИО эксперта]</t>
+          <t>Марина Ковалёва</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Специалист по косметологическому оборудованию, Medford · Опыт [N лет]</t>
+          <t>Специалист по косметологическому оборудованию, Medford · Опыт [N лет] · ФИО — рандомный плейсхолдер, заменить</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка товаров — по всей России. Гарантия — от 12 месяцев с сервисной поддержкой; предоставляется обучение работе на аппарате. ООО «Медфорд» работает с 2009 года. Телефон для консультаций: [телефон].</t>
+          <t>Оплата — по счёту для юридических лиц и ИП. Доставка товаров — по всей России. Гарантия — от 12 месяцев с сервисной поддержкой; предоставляется обучение работе на аппарате. ООО «Медфорд» работает с 2009 года. Телефон для консультаций: +7 (499) 495-48-21.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">

--- a/medford_kosmetologiya_v2.xlsx
+++ b/medford_kosmetologiya_v2.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_SECTION_UF" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_BLOCKS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_PRODUCTS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_COMPARE_ROWS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CONTENT_ITEMS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_TECHNOLOGIES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_RATING" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_CASES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_FAQ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_FIELD_MAP" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_ENUMS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-1_Under_Hero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_BLOCKS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_PRODUCTS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_COMPARE_ROWS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CONTENT_ITEMS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_TECHNOLOGIES" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_RATING" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_CASES" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_FAQ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_FIELD_MAP" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_ENUMS" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="007F6000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -114,6 +119,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -817,6 +825,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>08_CASES — Кейсы оснащения (ПЛЕЙСХОЛДЕРЫ — заполнить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>IBLOCK_ID</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ELEMENT_XML_ID</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE *</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SORT *</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>NAME *</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>PROPERTY_SECTION_CODE *</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>PROPERTY_BLOCK_CODE *</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>PROPERTY_CASE_PAGE_URL *</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_CASE_ELEMENT_XML_ID</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_CARD_TITLE_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_LABEL_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_CLINIC_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_EQUIPMENT_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_DELIVERY_TIME_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_SERVICES_OVERRIDE</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY_IMAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SALON_1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>[Кейс: оснащение салона красоты]</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>kosmetologiya</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>CASES</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>[URL кейса]</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[Оснащение салона красоты — комбайн + RF]</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>[Проект, год]</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>[Салон, город]</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>[перечень аппаратов]</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>[срок]</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Подбор, доставка, обучение</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CASE_CLINIC_1</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[Кейс: косметологическая клиника]</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>kosmetologiya</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CASES</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[URL кейса]</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[Оснащение клиники — лазер + HIFU]</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[Проект, год]</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>[Клиника, город]</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>[перечень аппаратов]</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>[срок]</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Подбор, монтаж, обучение, сервис</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>CASE_CABINET_1</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>[Кейс: косметологический кабинет]</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>kosmetologiya</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CASES</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>[URL кейса]</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[Старт кабинета — ультразвук + микротоки]</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>[Проект, год]</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>[Кабинет, город]</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>[перечень аппаратов]</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>[срок]</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Подбор для старта, обучение</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ACTIVE=N: активировать после заполнения реальными данными. Не публиковать вымышленные кейсы (методика: не фабриковать).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1191,7 +1540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2243,7 +2592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3404,6 +3753,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Ввод в эксплуатацию</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Проведём пусконаладку, настройку протоколов и обучение работе с аппаратом</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Подготовка КП за 1 день</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Обратный звонок бесплатно</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Сервисное обслуживание и гарантия</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Гарантийное сопровождение, диагностика и поставка расходных материалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Подбор решения</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Подберём аппарат под задачи салона или клиники и бюджет закупки</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3886,7 +4314,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4469,7 +4897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4912,7 +5340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6072,7 +6500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6802,7 +7230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7123,345 +7551,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>08_CASES — Кейсы оснащения (ПЛЕЙСХОЛДЕРЫ — заполнить)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>IBLOCK_ID</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ELEMENT_XML_ID</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE *</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SORT *</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>NAME *</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>PROPERTY_SECTION_CODE *</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>PROPERTY_BLOCK_CODE *</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>PROPERTY_CASE_PAGE_URL *</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_CASE_ELEMENT_XML_ID</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_CARD_TITLE_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_LABEL_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_CLINIC_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_EQUIPMENT_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_DELIVERY_TIME_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_SERVICES_OVERRIDE</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY_IMAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SALON_1</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>[Кейс: оснащение салона красоты]</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>kosmetologiya</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>CASES</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>[URL кейса]</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>[Оснащение салона красоты — комбайн + RF]</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>[Проект, год]</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>[Салон, город]</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>[перечень аппаратов]</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>[срок]</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Подбор, доставка, обучение</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CASE_CLINIC_1</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[Кейс: косметологическая клиника]</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>kosmetologiya</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>CASES</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[URL кейса]</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[Оснащение клиники — лазер + HIFU]</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[Проект, год]</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[Клиника, город]</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>[перечень аппаратов]</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>[срок]</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Подбор, монтаж, обучение, сервис</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>CASE_CABINET_1</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>[Кейс: косметологический кабинет]</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>kosmetologiya</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>CASES</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>[URL кейса]</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>[Старт кабинета — ультразвук + микротоки]</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>[Проект, год]</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>[Кабинет, город]</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>[перечень аппаратов]</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>[срок]</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>Подбор для старта, обучение</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ACTIVE=N: активировать после заполнения реальными данными. Не публиковать вымышленные кейсы (методика: не фабриковать).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>